--- a/2024C/data/result1_2.xlsx
+++ b/2024C/data/result1_2.xlsx
@@ -854,11 +854,11 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n"/>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
@@ -1157,7 +1157,9 @@
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
+      <c r="E9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
@@ -1165,9 +1167,7 @@
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
       <c r="P9" s="9" t="n"/>
@@ -1311,15 +1311,17 @@
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
+      <c r="F12" s="8" t="n">
+        <v>0.505</v>
+      </c>
       <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
+      <c r="H12" s="8" t="n">
+        <v>24.495</v>
+      </c>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
       <c r="O12" s="8" t="n"/>
@@ -1417,11 +1419,11 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
@@ -1470,10 +1472,10 @@
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n">
+      <c r="L15" s="9" t="n">
         <v>44</v>
       </c>
+      <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
@@ -1567,15 +1569,15 @@
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
+      <c r="G17" s="9" t="n">
+        <v>24.95</v>
+      </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
@@ -1674,10 +1676,10 @@
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9" t="n">
+      <c r="L19" s="9" t="n">
         <v>45</v>
       </c>
+      <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
@@ -1718,16 +1720,16 @@
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
+      <c r="L20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
@@ -1821,7 +1823,9 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
+      <c r="F22" s="8" t="n">
+        <v>14.075</v>
+      </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
@@ -1829,10 +1833,10 @@
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="O22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n">
+        <v>0.646</v>
+      </c>
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="8" t="n"/>
       <c r="R22" s="8" t="n"/>
@@ -1921,9 +1925,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -1933,7 +1935,9 @@
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
+      <c r="N24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
@@ -1972,9 +1976,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
@@ -1983,7 +1985,9 @@
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
+      <c r="M25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n">
+      <c r="D26" s="8" t="n">
         <v>27</v>
       </c>
+      <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
@@ -3471,16 +3475,16 @@
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
       <c r="W54" s="8" t="n"/>
-      <c r="X54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X54" s="8" t="n"/>
       <c r="Y54" s="8" t="n"/>
       <c r="Z54" s="8" t="n"/>
       <c r="AA54" s="8" t="n"/>
       <c r="AB54" s="8" t="n"/>
       <c r="AC54" s="8" t="n"/>
       <c r="AD54" s="8" t="n"/>
-      <c r="AE54" s="8" t="n"/>
+      <c r="AE54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF54" s="8" t="n"/>
       <c r="AG54" s="8" t="n"/>
       <c r="AH54" s="8" t="n"/>
@@ -3522,16 +3526,16 @@
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
       <c r="W55" s="9" t="n"/>
-      <c r="X55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X55" s="9" t="n"/>
       <c r="Y55" s="9" t="n"/>
       <c r="Z55" s="9" t="n"/>
       <c r="AA55" s="9" t="n"/>
       <c r="AB55" s="9" t="n"/>
       <c r="AC55" s="9" t="n"/>
       <c r="AD55" s="9" t="n"/>
-      <c r="AE55" s="9" t="n"/>
+      <c r="AE55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
       <c r="AH55" s="9" t="n"/>
@@ -4880,16 +4884,16 @@
       <c r="U82" s="8" t="n"/>
       <c r="V82" s="8" t="n"/>
       <c r="W82" s="8" t="n"/>
-      <c r="X82" s="8" t="n"/>
+      <c r="X82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y82" s="8" t="n"/>
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
       <c r="AC82" s="8" t="n"/>
       <c r="AD82" s="8" t="n"/>
-      <c r="AE82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE82" s="8" t="n"/>
       <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
@@ -4930,16 +4934,16 @@
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
-      <c r="X83" s="9" t="n"/>
+      <c r="X83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y83" s="9" t="n"/>
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
       <c r="AC83" s="9" t="n"/>
       <c r="AD83" s="9" t="n"/>
-      <c r="AE83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
       <c r="AH83" s="9" t="n"/>
@@ -5326,13 +5330,13 @@
       </c>
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
+      <c r="E2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
       <c r="L2" s="8" t="n"/>
@@ -5427,16 +5431,16 @@
         </is>
       </c>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
+      <c r="D4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
-      <c r="K4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
@@ -5534,10 +5538,10 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n">
+      <c r="I6" s="8" t="n">
         <v>68</v>
       </c>
+      <c r="J6" s="8" t="n"/>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
@@ -5687,12 +5691,12 @@
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="L9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
@@ -5740,13 +5744,13 @@
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n"/>
+      <c r="O10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="P10" s="8" t="n"/>
       <c r="Q10" s="8" t="n"/>
       <c r="R10" s="8" t="n"/>
@@ -5791,11 +5795,11 @@
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+      <c r="K11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
@@ -5843,10 +5847,10 @@
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n">
+      <c r="L12" s="8" t="n">
         <v>25</v>
       </c>
+      <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
       <c r="O12" s="8" t="n"/>
       <c r="P12" s="8" t="n"/>
@@ -5940,12 +5944,14 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>55</v>
+        <v>53.064</v>
       </c>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="J14" s="8" t="n">
+        <v>1.936</v>
+      </c>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
@@ -5988,7 +5994,9 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
@@ -5999,9 +6007,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
-      <c r="O15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
@@ -6042,7 +6048,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>45.121</v>
+        <v>47.919</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -6053,7 +6059,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>4.879</v>
+        <v>2.081</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -6092,9 +6098,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n"/>
@@ -6102,7 +6106,9 @@
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
+      <c r="L17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
@@ -6147,10 +6153,10 @@
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
@@ -6194,7 +6200,9 @@
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -6205,9 +6213,7 @@
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
-      <c r="O19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
@@ -6248,16 +6254,18 @@
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
+      <c r="G20" s="8" t="n">
+        <v>21.403</v>
+      </c>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
+      <c r="N20" s="8" t="n">
+        <v>13.597</v>
+      </c>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="n"/>
@@ -6296,7 +6304,9 @@
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
@@ -6304,9 +6314,7 @@
       <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
-      <c r="L21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
@@ -6347,20 +6355,18 @@
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n">
-        <v>9.667</v>
-      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n">
-        <v>5.333</v>
-      </c>
+      <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
+      <c r="M22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
@@ -6458,12 +6464,12 @@
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
+      <c r="K24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
@@ -6502,7 +6508,9 @@
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
@@ -6510,9 +6518,7 @@
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
@@ -6561,10 +6567,10 @@
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
-      <c r="L26" s="8" t="n">
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n"/>
       <c r="P26" s="8" t="n"/>
@@ -6611,10 +6617,10 @@
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="9" t="n">
+      <c r="K27" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
       <c r="O27" s="9" t="n"/>
@@ -6672,7 +6678,9 @@
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n"/>
       <c r="T28" s="8" t="n"/>
-      <c r="U28" s="8" t="n"/>
+      <c r="U28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
       <c r="X28" s="8" t="n"/>
@@ -6682,9 +6690,7 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n"/>
-      <c r="AE28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
       <c r="AG28" s="8" t="n"/>
       <c r="AH28" s="8" t="n"/>
@@ -6721,7 +6727,9 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n"/>
+      <c r="S29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
@@ -6733,9 +6741,7 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n"/>
-      <c r="AE29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
       <c r="AG29" s="9" t="n"/>
       <c r="AH29" s="9" t="n"/>
@@ -6774,7 +6780,9 @@
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
-      <c r="U30" s="8" t="n"/>
+      <c r="U30" s="8" t="n">
+        <v>0.173</v>
+      </c>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
@@ -6784,12 +6792,12 @@
       <c r="AB30" s="8" t="n"/>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
-      <c r="AE30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="AE30" s="8" t="n"/>
       <c r="AF30" s="8" t="n"/>
       <c r="AG30" s="8" t="n"/>
-      <c r="AH30" s="8" t="n"/>
+      <c r="AH30" s="8" t="n">
+        <v>13.827</v>
+      </c>
       <c r="AI30" s="8" t="n"/>
       <c r="AJ30" s="8" t="n"/>
       <c r="AK30" s="8" t="n"/>
@@ -6823,21 +6831,23 @@
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="n"/>
+      <c r="S31" s="9" t="n">
+        <v>0.918</v>
+      </c>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
       <c r="W31" s="9" t="n"/>
-      <c r="X31" s="9" t="n"/>
+      <c r="X31" s="9" t="n">
+        <v>5.082</v>
+      </c>
       <c r="Y31" s="9" t="n"/>
       <c r="Z31" s="9" t="n"/>
       <c r="AA31" s="9" t="n"/>
       <c r="AB31" s="9" t="n"/>
       <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="9" t="n"/>
-      <c r="AE31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="AE31" s="9" t="n"/>
       <c r="AF31" s="9" t="n"/>
       <c r="AG31" s="9" t="n"/>
       <c r="AH31" s="9" t="n"/>
@@ -6978,7 +6988,9 @@
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
-      <c r="U34" s="8" t="n"/>
+      <c r="U34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
@@ -6988,9 +7000,7 @@
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
-      <c r="AE34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
       <c r="AG34" s="8" t="n"/>
       <c r="AH34" s="8" t="n"/>
@@ -7029,7 +7039,9 @@
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
-      <c r="U35" s="9" t="n"/>
+      <c r="U35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
@@ -7039,9 +7051,7 @@
       <c r="AB35" s="9" t="n"/>
       <c r="AC35" s="9" t="n"/>
       <c r="AD35" s="9" t="n"/>
-      <c r="AE35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
@@ -7131,7 +7141,9 @@
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
-      <c r="U37" s="9" t="n"/>
+      <c r="U37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="9" t="n"/>
@@ -7141,9 +7153,7 @@
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE37" s="9" t="n"/>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n"/>
@@ -7182,7 +7192,9 @@
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n"/>
       <c r="T38" s="8" t="n"/>
-      <c r="U38" s="8" t="n"/>
+      <c r="U38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
       <c r="X38" s="8" t="n"/>
@@ -7192,9 +7204,7 @@
       <c r="AB38" s="8" t="n"/>
       <c r="AC38" s="8" t="n"/>
       <c r="AD38" s="8" t="n"/>
-      <c r="AE38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE38" s="8" t="n"/>
       <c r="AF38" s="8" t="n"/>
       <c r="AG38" s="8" t="n"/>
       <c r="AH38" s="8" t="n"/>
@@ -7233,7 +7243,9 @@
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
-      <c r="U39" s="9" t="n"/>
+      <c r="U39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
@@ -7243,9 +7255,7 @@
       <c r="AB39" s="9" t="n"/>
       <c r="AC39" s="9" t="n"/>
       <c r="AD39" s="9" t="n"/>
-      <c r="AE39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE39" s="9" t="n"/>
       <c r="AF39" s="9" t="n"/>
       <c r="AG39" s="9" t="n"/>
       <c r="AH39" s="9" t="n"/>
@@ -7284,7 +7294,9 @@
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
-      <c r="U40" s="8" t="n"/>
+      <c r="U40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
@@ -7294,9 +7306,7 @@
       <c r="AB40" s="8" t="n"/>
       <c r="AC40" s="8" t="n"/>
       <c r="AD40" s="8" t="n"/>
-      <c r="AE40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE40" s="8" t="n"/>
       <c r="AF40" s="8" t="n"/>
       <c r="AG40" s="8" t="n"/>
       <c r="AH40" s="8" t="n"/>
@@ -7335,7 +7345,9 @@
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
-      <c r="U41" s="9" t="n"/>
+      <c r="U41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n"/>
@@ -7345,9 +7357,7 @@
       <c r="AB41" s="9" t="n"/>
       <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9" t="n"/>
-      <c r="AE41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE41" s="9" t="n"/>
       <c r="AF41" s="9" t="n"/>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="9" t="n"/>
@@ -7641,7 +7651,9 @@
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
-      <c r="U47" s="9" t="n"/>
+      <c r="U47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
       <c r="X47" s="9" t="n"/>
@@ -7651,9 +7663,7 @@
       <c r="AB47" s="9" t="n"/>
       <c r="AC47" s="9" t="n"/>
       <c r="AD47" s="9" t="n"/>
-      <c r="AE47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE47" s="9" t="n"/>
       <c r="AF47" s="9" t="n"/>
       <c r="AG47" s="9" t="n"/>
       <c r="AH47" s="9" t="n"/>
@@ -7692,7 +7702,9 @@
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n"/>
       <c r="T48" s="8" t="n"/>
-      <c r="U48" s="8" t="n"/>
+      <c r="U48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
       <c r="X48" s="8" t="n"/>
@@ -7702,9 +7714,7 @@
       <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="n"/>
-      <c r="AE48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE48" s="8" t="n"/>
       <c r="AF48" s="8" t="n"/>
       <c r="AG48" s="8" t="n"/>
       <c r="AH48" s="8" t="n"/>
@@ -7794,7 +7804,9 @@
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n"/>
       <c r="T50" s="8" t="n"/>
-      <c r="U50" s="8" t="n"/>
+      <c r="U50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V50" s="8" t="n"/>
       <c r="W50" s="8" t="n"/>
       <c r="X50" s="8" t="n"/>
@@ -7804,9 +7816,7 @@
       <c r="AB50" s="8" t="n"/>
       <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="n"/>
-      <c r="AE50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE50" s="8" t="n"/>
       <c r="AF50" s="8" t="n"/>
       <c r="AG50" s="8" t="n"/>
       <c r="AH50" s="8" t="n"/>
@@ -7845,7 +7855,9 @@
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n"/>
       <c r="T51" s="9" t="n"/>
-      <c r="U51" s="9" t="n"/>
+      <c r="U51" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
@@ -7855,9 +7867,7 @@
       <c r="AB51" s="9" t="n"/>
       <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9" t="n"/>
-      <c r="AE51" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE51" s="9" t="n"/>
       <c r="AF51" s="9" t="n"/>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n"/>
@@ -7894,14 +7904,14 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n"/>
+      <c r="S52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X52" s="8" t="n"/>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
@@ -7996,9 +8006,7 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S54" s="8" t="n"/>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
@@ -8010,7 +8018,9 @@
       <c r="AB54" s="8" t="n"/>
       <c r="AC54" s="8" t="n"/>
       <c r="AD54" s="8" t="n"/>
-      <c r="AE54" s="8" t="n"/>
+      <c r="AE54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF54" s="8" t="n"/>
       <c r="AG54" s="8" t="n"/>
       <c r="AH54" s="8" t="n"/>
@@ -8047,9 +8057,7 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S55" s="9" t="n"/>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
@@ -8061,7 +8069,9 @@
       <c r="AB55" s="9" t="n"/>
       <c r="AC55" s="9" t="n"/>
       <c r="AD55" s="9" t="n"/>
-      <c r="AE55" s="9" t="n"/>
+      <c r="AE55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
       <c r="AH55" s="9" t="n"/>
@@ -8124,10 +8134,10 @@
       <c r="AI56" s="8" t="n"/>
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n"/>
-      <c r="AL56" s="8" t="n"/>
-      <c r="AM56" s="8" t="n">
+      <c r="AL56" s="8" t="n">
         <v>15</v>
       </c>
+      <c r="AM56" s="8" t="n"/>
       <c r="AN56" s="8" t="n"/>
       <c r="AO56" s="8" t="n"/>
       <c r="AP56" s="8" t="n"/>
@@ -8224,7 +8234,7 @@
       <c r="AI58" s="8" t="n"/>
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n">
-        <v>14</v>
+        <v>13.909</v>
       </c>
       <c r="AL58" s="8" t="n"/>
       <c r="AM58" s="8" t="n"/>
@@ -8274,7 +8284,7 @@
       <c r="AI59" s="9" t="n"/>
       <c r="AJ59" s="9" t="n"/>
       <c r="AK59" s="9" t="n">
-        <v>6</v>
+        <v>5.998</v>
       </c>
       <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n"/>
@@ -8374,10 +8384,10 @@
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="9" t="n"/>
       <c r="AK61" s="9" t="n"/>
-      <c r="AL61" s="9" t="n">
+      <c r="AL61" s="9" t="n"/>
+      <c r="AM61" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="AM61" s="9" t="n"/>
       <c r="AN61" s="9" t="n"/>
       <c r="AO61" s="9" t="n"/>
       <c r="AP61" s="9" t="n"/>
@@ -8475,7 +8485,7 @@
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
       <c r="AL63" s="9" t="n">
-        <v>20</v>
+        <v>19.923</v>
       </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
@@ -8627,7 +8637,7 @@
       <c r="AL66" s="8" t="n"/>
       <c r="AM66" s="8" t="n"/>
       <c r="AN66" s="8" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="AO66" s="8" t="n"/>
       <c r="AP66" s="8" t="n"/>
@@ -8727,9 +8737,11 @@
       <c r="AL68" s="8" t="n"/>
       <c r="AM68" s="8" t="n"/>
       <c r="AN68" s="8" t="n"/>
-      <c r="AO68" s="8" t="n"/>
+      <c r="AO68" s="8" t="n">
+        <v>0.022</v>
+      </c>
       <c r="AP68" s="8" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AQ68" s="8" t="n"/>
     </row>
@@ -8779,7 +8791,7 @@
       <c r="AN69" s="9" t="n"/>
       <c r="AO69" s="9" t="n"/>
       <c r="AP69" s="9" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="AQ69" s="9" t="n"/>
     </row>
@@ -9077,9 +9089,11 @@
       <c r="AL75" s="9" t="n"/>
       <c r="AM75" s="9" t="n"/>
       <c r="AN75" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO75" s="9" t="n"/>
+        <v>0.597</v>
+      </c>
+      <c r="AO75" s="9" t="n">
+        <v>0.003</v>
+      </c>
       <c r="AP75" s="9" t="n"/>
       <c r="AQ75" s="9" t="n"/>
     </row>
@@ -9127,7 +9141,7 @@
       <c r="AL76" s="8" t="n"/>
       <c r="AM76" s="8" t="n"/>
       <c r="AN76" s="8" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="AO76" s="8" t="n"/>
       <c r="AP76" s="8" t="n"/>
@@ -9227,7 +9241,7 @@
       <c r="AL78" s="8" t="n"/>
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="AO78" s="8" t="n"/>
       <c r="AP78" s="8" t="n"/>
@@ -9310,7 +9324,9 @@
       <c r="U80" s="8" t="n"/>
       <c r="V80" s="8" t="n"/>
       <c r="W80" s="8" t="n"/>
-      <c r="X80" s="8" t="n"/>
+      <c r="X80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
@@ -9320,9 +9336,7 @@
       <c r="AE80" s="8" t="n"/>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
-      <c r="AH80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH80" s="8" t="n"/>
       <c r="AI80" s="8" t="n"/>
       <c r="AJ80" s="8" t="n"/>
       <c r="AK80" s="8" t="n"/>
@@ -9856,13 +9870,13 @@
       </c>
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n">
-        <v>80</v>
-      </c>
+      <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
+      <c r="I2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
       <c r="L2" s="8" t="n"/>
@@ -9907,15 +9921,15 @@
       </c>
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
+      <c r="E3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
       <c r="H3" s="9" t="n"/>
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="K3" s="9" t="n"/>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
@@ -9957,16 +9971,16 @@
         </is>
       </c>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
-      <c r="K4" s="8" t="n"/>
+      <c r="K4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
@@ -10114,10 +10128,10 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="I7" s="9" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -10166,10 +10180,10 @@
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
@@ -10212,9 +10226,7 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -10225,7 +10237,9 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
-      <c r="O9" s="9" t="n"/>
+      <c r="O9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="P9" s="9" t="n"/>
       <c r="Q9" s="9" t="n"/>
       <c r="R9" s="9" t="n"/>
@@ -10368,15 +10382,15 @@
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
+      <c r="M12" s="8" t="n">
+        <v>25</v>
+      </c>
       <c r="N12" s="8" t="n"/>
       <c r="O12" s="8" t="n"/>
       <c r="P12" s="8" t="n"/>
@@ -10471,13 +10485,13 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
@@ -10518,9 +10532,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
@@ -10528,7 +10540,9 @@
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
+      <c r="L15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
@@ -10574,13 +10588,13 @@
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n">
-        <v>50</v>
-      </c>
+      <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
+      <c r="M16" s="8" t="n">
+        <v>50</v>
+      </c>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n"/>
       <c r="P16" s="8" t="n"/>
@@ -10722,9 +10736,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -10732,7 +10744,9 @@
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
+      <c r="L19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
@@ -10781,10 +10795,10 @@
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n">
+      <c r="L20" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
@@ -10825,9 +10839,7 @@
       </c>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
@@ -10835,7 +10847,9 @@
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
+      <c r="M21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
@@ -10878,7 +10892,7 @@
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n">
-        <v>2</v>
+        <v>1.654</v>
       </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
@@ -10888,7 +10902,7 @@
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n">
-        <v>13</v>
+        <v>13.346</v>
       </c>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
@@ -10931,7 +10945,7 @@
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n">
-        <v>12.794</v>
+        <v>12.667</v>
       </c>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
@@ -10979,7 +10993,9 @@
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="D24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -10988,9 +11004,7 @@
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
@@ -11088,11 +11102,11 @@
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
+      <c r="K26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="L26" s="8" t="n"/>
-      <c r="M26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n"/>
       <c r="P26" s="8" t="n"/>
@@ -11200,9 +11214,7 @@
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n"/>
       <c r="T28" s="8" t="n"/>
-      <c r="U28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
       <c r="X28" s="8" t="n"/>
@@ -11212,7 +11224,9 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n"/>
-      <c r="AE28" s="8" t="n"/>
+      <c r="AE28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="AF28" s="8" t="n"/>
       <c r="AG28" s="8" t="n"/>
       <c r="AH28" s="8" t="n"/>
@@ -11251,9 +11265,7 @@
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
-      <c r="U29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
       <c r="W29" s="9" t="n"/>
       <c r="X29" s="9" t="n"/>
@@ -11263,7 +11275,9 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n"/>
-      <c r="AE29" s="9" t="n"/>
+      <c r="AE29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="AF29" s="9" t="n"/>
       <c r="AG29" s="9" t="n"/>
       <c r="AH29" s="9" t="n"/>
@@ -11302,9 +11316,7 @@
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
-      <c r="U30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
@@ -11314,7 +11326,9 @@
       <c r="AB30" s="8" t="n"/>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
-      <c r="AE30" s="8" t="n"/>
+      <c r="AE30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="AF30" s="8" t="n"/>
       <c r="AG30" s="8" t="n"/>
       <c r="AH30" s="8" t="n"/>
@@ -11353,9 +11367,7 @@
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
-      <c r="U31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
       <c r="W31" s="9" t="n"/>
       <c r="X31" s="9" t="n"/>
@@ -11365,7 +11377,9 @@
       <c r="AB31" s="9" t="n"/>
       <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="9" t="n"/>
-      <c r="AE31" s="9" t="n"/>
+      <c r="AE31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="AF31" s="9" t="n"/>
       <c r="AG31" s="9" t="n"/>
       <c r="AH31" s="9" t="n"/>
@@ -11506,9 +11520,7 @@
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
-      <c r="U34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
@@ -11518,7 +11530,9 @@
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
-      <c r="AE34" s="8" t="n"/>
+      <c r="AE34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="AF34" s="8" t="n"/>
       <c r="AG34" s="8" t="n"/>
       <c r="AH34" s="8" t="n"/>
@@ -11557,9 +11571,7 @@
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
-      <c r="U35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
@@ -11569,7 +11581,9 @@
       <c r="AB35" s="9" t="n"/>
       <c r="AC35" s="9" t="n"/>
       <c r="AD35" s="9" t="n"/>
-      <c r="AE35" s="9" t="n"/>
+      <c r="AE35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
@@ -11659,9 +11673,7 @@
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
-      <c r="U37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="9" t="n"/>
@@ -11671,7 +11683,9 @@
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="9" t="n"/>
+      <c r="AE37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n"/>
@@ -11710,9 +11724,7 @@
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n"/>
       <c r="T38" s="8" t="n"/>
-      <c r="U38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
       <c r="X38" s="8" t="n"/>
@@ -11722,7 +11734,9 @@
       <c r="AB38" s="8" t="n"/>
       <c r="AC38" s="8" t="n"/>
       <c r="AD38" s="8" t="n"/>
-      <c r="AE38" s="8" t="n"/>
+      <c r="AE38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF38" s="8" t="n"/>
       <c r="AG38" s="8" t="n"/>
       <c r="AH38" s="8" t="n"/>
@@ -11761,9 +11775,7 @@
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
-      <c r="U39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
@@ -11773,7 +11785,9 @@
       <c r="AB39" s="9" t="n"/>
       <c r="AC39" s="9" t="n"/>
       <c r="AD39" s="9" t="n"/>
-      <c r="AE39" s="9" t="n"/>
+      <c r="AE39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF39" s="9" t="n"/>
       <c r="AG39" s="9" t="n"/>
       <c r="AH39" s="9" t="n"/>
@@ -11812,9 +11826,7 @@
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
-      <c r="U40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
@@ -11824,7 +11836,9 @@
       <c r="AB40" s="8" t="n"/>
       <c r="AC40" s="8" t="n"/>
       <c r="AD40" s="8" t="n"/>
-      <c r="AE40" s="8" t="n"/>
+      <c r="AE40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF40" s="8" t="n"/>
       <c r="AG40" s="8" t="n"/>
       <c r="AH40" s="8" t="n"/>
@@ -11863,9 +11877,7 @@
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
-      <c r="U41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n"/>
@@ -11875,7 +11887,9 @@
       <c r="AB41" s="9" t="n"/>
       <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9" t="n"/>
-      <c r="AE41" s="9" t="n"/>
+      <c r="AE41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF41" s="9" t="n"/>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="9" t="n"/>
@@ -12169,9 +12183,7 @@
       <c r="R47" s="9" t="n"/>
       <c r="S47" s="9" t="n"/>
       <c r="T47" s="9" t="n"/>
-      <c r="U47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
       <c r="X47" s="9" t="n"/>
@@ -12181,7 +12193,9 @@
       <c r="AB47" s="9" t="n"/>
       <c r="AC47" s="9" t="n"/>
       <c r="AD47" s="9" t="n"/>
-      <c r="AE47" s="9" t="n"/>
+      <c r="AE47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF47" s="9" t="n"/>
       <c r="AG47" s="9" t="n"/>
       <c r="AH47" s="9" t="n"/>
@@ -12220,9 +12234,7 @@
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n"/>
       <c r="T48" s="8" t="n"/>
-      <c r="U48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
       <c r="X48" s="8" t="n"/>
@@ -12232,7 +12244,9 @@
       <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="n"/>
-      <c r="AE48" s="8" t="n"/>
+      <c r="AE48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF48" s="8" t="n"/>
       <c r="AG48" s="8" t="n"/>
       <c r="AH48" s="8" t="n"/>
@@ -12322,9 +12336,7 @@
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n"/>
       <c r="T50" s="8" t="n"/>
-      <c r="U50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
       <c r="W50" s="8" t="n"/>
       <c r="X50" s="8" t="n"/>
@@ -12334,7 +12346,9 @@
       <c r="AB50" s="8" t="n"/>
       <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="n"/>
-      <c r="AE50" s="8" t="n"/>
+      <c r="AE50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF50" s="8" t="n"/>
       <c r="AG50" s="8" t="n"/>
       <c r="AH50" s="8" t="n"/>
@@ -12373,9 +12387,7 @@
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n"/>
       <c r="T51" s="9" t="n"/>
-      <c r="U51" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U51" s="9" t="n"/>
       <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
@@ -12385,7 +12397,9 @@
       <c r="AB51" s="9" t="n"/>
       <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9" t="n"/>
-      <c r="AE51" s="9" t="n"/>
+      <c r="AE51" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF51" s="9" t="n"/>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n"/>
@@ -12524,7 +12538,9 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
+      <c r="S54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
@@ -12536,9 +12552,7 @@
       <c r="AB54" s="8" t="n"/>
       <c r="AC54" s="8" t="n"/>
       <c r="AD54" s="8" t="n"/>
-      <c r="AE54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE54" s="8" t="n"/>
       <c r="AF54" s="8" t="n"/>
       <c r="AG54" s="8" t="n"/>
       <c r="AH54" s="8" t="n"/>
@@ -12588,7 +12602,7 @@
       <c r="AC55" s="9" t="n"/>
       <c r="AD55" s="9" t="n"/>
       <c r="AE55" s="9" t="n">
-        <v>0.6</v>
+        <v>0.587</v>
       </c>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
@@ -12651,10 +12665,10 @@
       <c r="AH56" s="8" t="n"/>
       <c r="AI56" s="8" t="n"/>
       <c r="AJ56" s="8" t="n"/>
-      <c r="AK56" s="8" t="n">
+      <c r="AK56" s="8" t="n"/>
+      <c r="AL56" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="AL56" s="8" t="n"/>
       <c r="AM56" s="8" t="n"/>
       <c r="AN56" s="8" t="n"/>
       <c r="AO56" s="8" t="n"/>
@@ -12902,7 +12916,7 @@
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="9" t="n"/>
       <c r="AK61" s="9" t="n">
-        <v>5</v>
+        <v>11.705</v>
       </c>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n"/>
@@ -12951,10 +12965,10 @@
       <c r="AH62" s="8" t="n"/>
       <c r="AI62" s="8" t="n"/>
       <c r="AJ62" s="8" t="n"/>
-      <c r="AK62" s="8" t="n">
+      <c r="AK62" s="8" t="n"/>
+      <c r="AL62" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
@@ -13055,11 +13069,13 @@
       <c r="AL64" s="8" t="n"/>
       <c r="AM64" s="8" t="n"/>
       <c r="AN64" s="8" t="n">
-        <v>0.6</v>
+        <v>0.589</v>
       </c>
       <c r="AO64" s="8" t="n"/>
       <c r="AP64" s="8" t="n"/>
-      <c r="AQ64" s="8" t="n"/>
+      <c r="AQ64" s="8" t="n">
+        <v>0.011</v>
+      </c>
     </row>
     <row r="65" ht="12" customHeight="1" s="19">
       <c r="B65" s="10" t="inlineStr">
@@ -13405,7 +13421,7 @@
       <c r="AL71" s="9" t="n"/>
       <c r="AM71" s="9" t="n"/>
       <c r="AN71" s="9" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="AO71" s="9" t="n"/>
       <c r="AP71" s="9" t="n"/>
@@ -13505,7 +13521,7 @@
       <c r="AL73" s="9" t="n"/>
       <c r="AM73" s="9" t="n"/>
       <c r="AN73" s="9" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="AO73" s="9" t="n"/>
       <c r="AP73" s="9" t="n"/>
@@ -13833,14 +13849,14 @@
       <c r="P80" s="8" t="n"/>
       <c r="Q80" s="8" t="n"/>
       <c r="R80" s="8" t="n"/>
-      <c r="S80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S80" s="8" t="n"/>
       <c r="T80" s="8" t="n"/>
       <c r="U80" s="8" t="n"/>
       <c r="V80" s="8" t="n"/>
       <c r="W80" s="8" t="n"/>
-      <c r="X80" s="8" t="n"/>
+      <c r="X80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
@@ -13939,7 +13955,7 @@
       <c r="V82" s="8" t="n"/>
       <c r="W82" s="8" t="n"/>
       <c r="X82" s="8" t="n">
-        <v>0.6</v>
+        <v>0.598</v>
       </c>
       <c r="Y82" s="8" t="n"/>
       <c r="Z82" s="8" t="n"/>
@@ -13983,14 +13999,14 @@
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n"/>
       <c r="R83" s="9" t="n"/>
-      <c r="S83" s="9" t="n"/>
+      <c r="S83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
-      <c r="X83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X83" s="9" t="n"/>
       <c r="Y83" s="9" t="n"/>
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
@@ -14493,10 +14509,10 @@
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
-      <c r="L4" s="8" t="n"/>
-      <c r="M4" s="8" t="n">
+      <c r="L4" s="8" t="n">
         <v>35</v>
       </c>
+      <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
       <c r="O4" s="8" t="n"/>
       <c r="P4" s="8" t="n"/>
@@ -14740,7 +14756,9 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="D9" s="9" t="n">
+        <v>46</v>
+      </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -14749,9 +14767,7 @@
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n">
-        <v>46</v>
-      </c>
+      <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
       <c r="P9" s="9" t="n"/>
@@ -14799,10 +14815,10 @@
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
       <c r="O10" s="8" t="n"/>
       <c r="P10" s="8" t="n"/>
@@ -14998,7 +15014,7 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>55</v>
+        <v>54.444</v>
       </c>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
@@ -15054,10 +15070,10 @@
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
@@ -15100,7 +15116,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>45.121</v>
+        <v>38.306</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -15111,7 +15127,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>4.879</v>
+        <v>11.519</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -15153,15 +15169,15 @@
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
+      <c r="G17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
@@ -15304,9 +15320,7 @@
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
@@ -15316,7 +15330,9 @@
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="O20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="n"/>
       <c r="R20" s="8" t="n"/>
@@ -15355,7 +15371,9 @@
       </c>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
+      <c r="E21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
@@ -15365,9 +15383,7 @@
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
@@ -15465,10 +15481,10 @@
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n">
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
@@ -18911,10 +18927,10 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n">
+      <c r="D2" s="8" t="n">
         <v>80</v>
       </c>
+      <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
@@ -18963,12 +18979,12 @@
       </c>
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="E3" s="9" t="n"/>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
+      <c r="H3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n"/>
@@ -19013,16 +19029,16 @@
         </is>
       </c>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
+      <c r="D4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
-      <c r="K4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
@@ -19120,11 +19136,11 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n"/>
@@ -19167,7 +19183,7 @@
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n">
-        <v>43.7</v>
+        <v>44.212</v>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -19180,7 +19196,7 @@
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n">
-        <v>11.3</v>
+        <v>10.788</v>
       </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
@@ -19270,10 +19286,10 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
@@ -19321,7 +19337,9 @@
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
@@ -19330,9 +19348,7 @@
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
       <c r="O10" s="8" t="n"/>
       <c r="P10" s="8" t="n"/>
@@ -19372,16 +19388,16 @@
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="D11" s="9" t="n">
+        <v>28</v>
+      </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n">
-        <v>28</v>
-      </c>
+      <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
@@ -19427,7 +19443,7 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>25</v>
+        <v>24.959</v>
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -19477,7 +19493,7 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n">
-        <v>86</v>
+        <v>85.994</v>
       </c>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
@@ -19529,13 +19545,13 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
+      <c r="L14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
@@ -19576,7 +19592,9 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="9" t="n">
+        <v>44</v>
+      </c>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
@@ -19585,9 +19603,7 @@
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n">
-        <v>44</v>
-      </c>
+      <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
@@ -19678,9 +19694,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n">
-        <v>25</v>
-      </c>
+      <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n"/>
@@ -19691,7 +19705,9 @@
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n"/>
+      <c r="O17" s="9" t="n">
+        <v>25</v>
+      </c>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
@@ -19729,7 +19745,9 @@
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="D18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
@@ -19737,9 +19755,7 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n">
-        <v>60</v>
-      </c>
+      <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
@@ -19780,7 +19796,9 @@
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
@@ -19791,9 +19809,7 @@
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
-      <c r="O19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
@@ -19882,7 +19898,9 @@
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
@@ -19891,9 +19909,7 @@
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
@@ -19933,10 +19949,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
@@ -19986,7 +20002,9 @@
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
+      <c r="F23" s="9" t="n">
+        <v>12.987</v>
+      </c>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
@@ -19994,9 +20012,7 @@
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
@@ -20035,9 +20051,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
@@ -20046,7 +20060,9 @@
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
+      <c r="M24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
@@ -20138,7 +20154,9 @@
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
+      <c r="E26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
@@ -20146,9 +20164,7 @@
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
-      <c r="M26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n"/>
       <c r="P26" s="8" t="n"/>
@@ -20254,11 +20270,11 @@
       <c r="P28" s="8" t="n"/>
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
-      <c r="S28" s="8" t="n"/>
+      <c r="S28" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="T28" s="8" t="n"/>
-      <c r="U28" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
       <c r="X28" s="8" t="n"/>
@@ -20307,7 +20323,9 @@
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
-      <c r="U29" s="9" t="n"/>
+      <c r="U29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="V29" s="9" t="n"/>
       <c r="W29" s="9" t="n"/>
       <c r="X29" s="9" t="n"/>
@@ -20317,9 +20335,7 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n"/>
-      <c r="AE29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
       <c r="AG29" s="9" t="n"/>
       <c r="AH29" s="9" t="n"/>
@@ -20356,11 +20372,11 @@
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
-      <c r="S30" s="8" t="n"/>
+      <c r="S30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="T30" s="8" t="n"/>
-      <c r="U30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
@@ -20409,7 +20425,9 @@
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
-      <c r="U31" s="9" t="n"/>
+      <c r="U31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="V31" s="9" t="n"/>
       <c r="W31" s="9" t="n"/>
       <c r="X31" s="9" t="n"/>
@@ -20419,9 +20437,7 @@
       <c r="AB31" s="9" t="n"/>
       <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="9" t="n"/>
-      <c r="AE31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="AE31" s="9" t="n"/>
       <c r="AF31" s="9" t="n"/>
       <c r="AG31" s="9" t="n"/>
       <c r="AH31" s="9" t="n"/>
@@ -20560,11 +20576,11 @@
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="n"/>
-      <c r="S34" s="8" t="n"/>
+      <c r="S34" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="T34" s="8" t="n"/>
-      <c r="U34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
@@ -20611,11 +20627,11 @@
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n"/>
+      <c r="S35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="T35" s="9" t="n"/>
-      <c r="U35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
@@ -20662,7 +20678,9 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
-      <c r="S36" s="8" t="n"/>
+      <c r="S36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
@@ -20674,9 +20692,7 @@
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
-      <c r="AE36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE36" s="8" t="n"/>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
       <c r="AH36" s="8" t="n"/>
@@ -20713,11 +20729,11 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
+      <c r="S37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T37" s="9" t="n"/>
-      <c r="U37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
       <c r="X37" s="9" t="n"/>
@@ -20764,11 +20780,11 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
-      <c r="S38" s="8" t="n"/>
+      <c r="S38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T38" s="8" t="n"/>
-      <c r="U38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
       <c r="X38" s="8" t="n"/>
@@ -20815,11 +20831,11 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n"/>
+      <c r="S39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T39" s="9" t="n"/>
-      <c r="U39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n"/>
@@ -20866,11 +20882,11 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
-      <c r="S40" s="8" t="n"/>
+      <c r="S40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T40" s="8" t="n"/>
-      <c r="U40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
@@ -20917,7 +20933,9 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n"/>
+      <c r="S41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
@@ -20929,9 +20947,7 @@
       <c r="AB41" s="9" t="n"/>
       <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9" t="n"/>
-      <c r="AE41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE41" s="9" t="n"/>
       <c r="AF41" s="9" t="n"/>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="9" t="n"/>
@@ -21123,7 +21139,9 @@
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
-      <c r="U45" s="9" t="n"/>
+      <c r="U45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
       <c r="X45" s="9" t="n"/>
@@ -21133,9 +21151,7 @@
       <c r="AB45" s="9" t="n"/>
       <c r="AC45" s="9" t="n"/>
       <c r="AD45" s="9" t="n"/>
-      <c r="AE45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE45" s="9" t="n"/>
       <c r="AF45" s="9" t="n"/>
       <c r="AG45" s="9" t="n"/>
       <c r="AH45" s="9" t="n"/>
@@ -21223,11 +21239,11 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
-      <c r="S47" s="9" t="n"/>
+      <c r="S47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T47" s="9" t="n"/>
-      <c r="U47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
       <c r="X47" s="9" t="n"/>
@@ -21274,11 +21290,11 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
-      <c r="S48" s="8" t="n"/>
+      <c r="S48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T48" s="8" t="n"/>
-      <c r="U48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
       <c r="X48" s="8" t="n"/>
@@ -21376,7 +21392,9 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
-      <c r="S50" s="8" t="n"/>
+      <c r="S50" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
@@ -21388,9 +21406,7 @@
       <c r="AB50" s="8" t="n"/>
       <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="n"/>
-      <c r="AE50" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE50" s="8" t="n"/>
       <c r="AF50" s="8" t="n"/>
       <c r="AG50" s="8" t="n"/>
       <c r="AH50" s="8" t="n"/>
@@ -21427,11 +21443,11 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
-      <c r="S51" s="9" t="n"/>
+      <c r="S51" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T51" s="9" t="n"/>
-      <c r="U51" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U51" s="9" t="n"/>
       <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
       <c r="X51" s="9" t="n"/>
@@ -21491,7 +21507,7 @@
       <c r="AC52" s="8" t="n"/>
       <c r="AD52" s="8" t="n"/>
       <c r="AE52" s="8" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="AF52" s="8" t="n"/>
       <c r="AG52" s="8" t="n"/>
@@ -21529,11 +21545,11 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n">
+      <c r="S53" s="9" t="n"/>
+      <c r="T53" s="9" t="n"/>
+      <c r="U53" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="T53" s="9" t="n"/>
-      <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
       <c r="X53" s="9" t="n"/>
@@ -21708,7 +21724,7 @@
       <c r="AI56" s="8" t="n"/>
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n">
-        <v>15</v>
+        <v>14.921</v>
       </c>
       <c r="AL56" s="8" t="n"/>
       <c r="AM56" s="8" t="n"/>
@@ -21809,7 +21825,7 @@
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n"/>
       <c r="AL58" s="8" t="n">
-        <v>14</v>
+        <v>13.998</v>
       </c>
       <c r="AM58" s="8" t="n"/>
       <c r="AN58" s="8" t="n"/>
@@ -21908,7 +21924,7 @@
       <c r="AI60" s="8" t="n"/>
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n">
-        <v>10</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="AL60" s="8" t="n"/>
       <c r="AM60" s="8" t="n"/>
@@ -21958,7 +21974,7 @@
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="9" t="n"/>
       <c r="AK61" s="9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n"/>
@@ -22058,7 +22074,7 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n">
-        <v>20</v>
+        <v>19.892</v>
       </c>
       <c r="AL63" s="9" t="n"/>
       <c r="AM63" s="9" t="n"/>
@@ -22111,7 +22127,7 @@
       <c r="AL64" s="8" t="n"/>
       <c r="AM64" s="8" t="n"/>
       <c r="AN64" s="8" t="n">
-        <v>0.6</v>
+        <v>0.596</v>
       </c>
       <c r="AO64" s="8" t="n"/>
       <c r="AP64" s="8" t="n"/>
@@ -22313,7 +22329,7 @@
       <c r="AN68" s="8" t="n"/>
       <c r="AO68" s="8" t="n"/>
       <c r="AP68" s="8" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="AQ68" s="8" t="n"/>
     </row>
@@ -22561,7 +22577,7 @@
       <c r="AL73" s="9" t="n"/>
       <c r="AM73" s="9" t="n"/>
       <c r="AN73" s="9" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="AO73" s="9" t="n"/>
       <c r="AP73" s="9" t="n"/>
@@ -22711,7 +22727,7 @@
       <c r="AL76" s="8" t="n"/>
       <c r="AM76" s="8" t="n"/>
       <c r="AN76" s="8" t="n">
-        <v>0.6</v>
+        <v>0.592</v>
       </c>
       <c r="AO76" s="8" t="n"/>
       <c r="AP76" s="8" t="n"/>
@@ -22761,7 +22777,7 @@
       <c r="AL77" s="9" t="n"/>
       <c r="AM77" s="9" t="n"/>
       <c r="AN77" s="9" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="AO77" s="9" t="n"/>
       <c r="AP77" s="9" t="n"/>
@@ -22989,11 +23005,11 @@
       <c r="P82" s="8" t="n"/>
       <c r="Q82" s="8" t="n"/>
       <c r="R82" s="8" t="n"/>
-      <c r="S82" s="8" t="n">
+      <c r="S82" s="8" t="n"/>
+      <c r="T82" s="8" t="n"/>
+      <c r="U82" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="T82" s="8" t="n"/>
-      <c r="U82" s="8" t="n"/>
       <c r="V82" s="8" t="n"/>
       <c r="W82" s="8" t="n"/>
       <c r="X82" s="8" t="n"/>
@@ -23443,11 +23459,11 @@
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
+      <c r="H2" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n">
-        <v>79.67100000000001</v>
-      </c>
+      <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
       <c r="L2" s="8" t="n"/>
       <c r="M2" s="8" t="n"/>
@@ -23490,13 +23506,13 @@
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
+      <c r="D3" s="9" t="n">
+        <v>55</v>
+      </c>
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="H3" s="9" t="n"/>
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n"/>
@@ -23541,9 +23557,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
@@ -23554,7 +23568,9 @@
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
       <c r="N4" s="8" t="n"/>
-      <c r="O4" s="8" t="n"/>
+      <c r="O4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="P4" s="8" t="n"/>
       <c r="Q4" s="8" t="n"/>
       <c r="R4" s="8" t="n"/>
@@ -23598,7 +23614,7 @@
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n">
-        <v>71.76300000000001</v>
+        <v>72</v>
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
@@ -23645,7 +23661,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n">
-        <v>46.389</v>
+        <v>51.518</v>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -23655,7 +23671,7 @@
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n">
-        <v>21.611</v>
+        <v>16.482</v>
       </c>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -23803,7 +23819,7 @@
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n">
-        <v>46</v>
+        <v>45.726</v>
       </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -23848,18 +23864,16 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
-        <v>5.192</v>
-      </c>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n">
-        <v>34.808</v>
-      </c>
+      <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="J10" s="8" t="n">
+        <v>39.799</v>
+      </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -23901,15 +23915,13 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
-        <v>0.641</v>
-      </c>
+      <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n">
-        <v>27.038</v>
+        <v>28</v>
       </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -23954,9 +23966,7 @@
           <t>B5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>1.379</v>
-      </c>
+      <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
@@ -23966,7 +23976,7 @@
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n">
-        <v>23.621</v>
+        <v>25</v>
       </c>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
@@ -24109,23 +24119,21 @@
           <t>B8</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
-        <v>2.114</v>
-      </c>
+      <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="J15" s="9" t="n">
+        <v>43.992</v>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
-      <c r="O15" s="9" t="n">
-        <v>41.886</v>
-      </c>
+      <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
       <c r="Q15" s="9" t="n"/>
       <c r="R15" s="9" t="n"/>
@@ -24166,7 +24174,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>44.845</v>
+        <v>45.677</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -24177,7 +24185,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>5.155</v>
+        <v>4.323</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -24220,7 +24228,7 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
-        <v>24.666</v>
+        <v>24.758</v>
       </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -24269,18 +24277,16 @@
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n">
-        <v>4.469</v>
-      </c>
+      <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n">
-        <v>55.531</v>
-      </c>
+      <c r="K18" s="8" t="n"/>
       <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
+      <c r="M18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n"/>
@@ -24320,16 +24326,16 @@
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+      <c r="K19" s="9" t="n">
+        <v>45</v>
+      </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
@@ -24422,9 +24428,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
@@ -24434,7 +24438,9 @@
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
+      <c r="N21" s="9" t="n">
+        <v>19.211</v>
+      </c>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
@@ -24480,7 +24486,7 @@
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n">
-        <v>15</v>
+        <v>14.844</v>
       </c>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
@@ -24523,9 +24529,7 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>0.436</v>
-      </c>
+      <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -24539,7 +24543,7 @@
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n">
-        <v>12.564</v>
+        <v>12.757</v>
       </c>
       <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
@@ -24584,14 +24588,14 @@
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
+      <c r="K24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
-      <c r="P24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
       <c r="R24" s="8" t="n"/>
       <c r="S24" s="8" t="n"/>
@@ -24688,7 +24692,7 @@
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n">
-        <v>26.59</v>
+        <v>26.975</v>
       </c>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
@@ -24739,10 +24743,10 @@
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n">
+      <c r="M27" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="N27" s="9" t="n"/>
       <c r="O27" s="9" t="n"/>
       <c r="P27" s="9" t="n"/>
       <c r="Q27" s="9" t="n"/>
@@ -24847,9 +24851,7 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="S29" s="9" t="n"/>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
@@ -24861,7 +24863,9 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n"/>
-      <c r="AE29" s="9" t="n"/>
+      <c r="AE29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="AF29" s="9" t="n"/>
       <c r="AG29" s="9" t="n"/>
       <c r="AH29" s="9" t="n"/>
@@ -24949,23 +24953,21 @@
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
       <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="n">
-        <v>1.851</v>
-      </c>
+      <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
       <c r="W31" s="9" t="n"/>
-      <c r="X31" s="9" t="n">
-        <v>4.149</v>
-      </c>
+      <c r="X31" s="9" t="n"/>
       <c r="Y31" s="9" t="n"/>
       <c r="Z31" s="9" t="n"/>
       <c r="AA31" s="9" t="n"/>
       <c r="AB31" s="9" t="n"/>
       <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="9" t="n"/>
-      <c r="AE31" s="9" t="n"/>
+      <c r="AE31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="AF31" s="9" t="n"/>
       <c r="AG31" s="9" t="n"/>
       <c r="AH31" s="9" t="n"/>
@@ -25207,9 +25209,7 @@
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
       <c r="S36" s="8" t="n"/>
-      <c r="T36" s="8" t="n">
-        <v>0.015</v>
-      </c>
+      <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
       <c r="W36" s="8" t="n"/>
@@ -25221,7 +25221,7 @@
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
       <c r="AE36" s="8" t="n">
-        <v>0.585</v>
+        <v>0.6</v>
       </c>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
@@ -25272,13 +25272,11 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.543</v>
+        <v>0.6</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n">
-        <v>0.057</v>
-      </c>
+      <c r="AH37" s="9" t="n"/>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -25465,9 +25463,7 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n">
-        <v>0.031</v>
-      </c>
+      <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
@@ -25480,7 +25476,7 @@
       <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9" t="n"/>
       <c r="AE41" s="9" t="n">
-        <v>0.569</v>
+        <v>0.6</v>
       </c>
       <c r="AF41" s="9" t="n"/>
       <c r="AG41" s="9" t="n"/>
@@ -25671,9 +25667,7 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n">
-        <v>0.014</v>
-      </c>
+      <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
@@ -25686,7 +25680,7 @@
       <c r="AC45" s="9" t="n"/>
       <c r="AD45" s="9" t="n"/>
       <c r="AE45" s="9" t="n">
-        <v>0.462</v>
+        <v>0.6</v>
       </c>
       <c r="AF45" s="9" t="n"/>
       <c r="AG45" s="9" t="n"/>
@@ -25928,9 +25922,7 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
-      <c r="S50" s="8" t="n">
-        <v>0.023</v>
-      </c>
+      <c r="S50" s="8" t="n"/>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
@@ -25943,7 +25935,7 @@
       <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="n"/>
       <c r="AE50" s="8" t="n">
-        <v>0.577</v>
+        <v>0.6</v>
       </c>
       <c r="AF50" s="8" t="n"/>
       <c r="AG50" s="8" t="n"/>
@@ -26261,11 +26253,11 @@
       <c r="AH56" s="8" t="n"/>
       <c r="AI56" s="8" t="n"/>
       <c r="AJ56" s="8" t="n"/>
-      <c r="AK56" s="8" t="n">
+      <c r="AK56" s="8" t="n"/>
+      <c r="AL56" s="8" t="n"/>
+      <c r="AM56" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="AL56" s="8" t="n"/>
-      <c r="AM56" s="8" t="n"/>
       <c r="AN56" s="8" t="n"/>
       <c r="AO56" s="8" t="n"/>
       <c r="AP56" s="8" t="n"/>
@@ -26312,7 +26304,7 @@
       <c r="AI57" s="9" t="n"/>
       <c r="AJ57" s="9" t="n"/>
       <c r="AK57" s="9" t="n">
-        <v>9.339</v>
+        <v>10</v>
       </c>
       <c r="AL57" s="9" t="n"/>
       <c r="AM57" s="9" t="n"/>
@@ -26361,11 +26353,11 @@
       <c r="AH58" s="8" t="n"/>
       <c r="AI58" s="8" t="n"/>
       <c r="AJ58" s="8" t="n"/>
-      <c r="AK58" s="8" t="n"/>
+      <c r="AK58" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="AL58" s="8" t="n"/>
-      <c r="AM58" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="AM58" s="8" t="n"/>
       <c r="AN58" s="8" t="n"/>
       <c r="AO58" s="8" t="n"/>
       <c r="AP58" s="8" t="n"/>
@@ -26917,7 +26909,7 @@
       <c r="AN69" s="9" t="n"/>
       <c r="AO69" s="9" t="n"/>
       <c r="AP69" s="9" t="n">
-        <v>0.589</v>
+        <v>0.6</v>
       </c>
       <c r="AQ69" s="9" t="n"/>
     </row>
@@ -27365,7 +27357,7 @@
       <c r="AL78" s="8" t="n"/>
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n">
-        <v>0.594</v>
+        <v>0.6</v>
       </c>
       <c r="AO78" s="8" t="n"/>
       <c r="AP78" s="8" t="n"/>
@@ -28046,7 +28038,7 @@
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="9" t="n">
-        <v>54.85</v>
+        <v>54.743</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
@@ -28145,15 +28137,13 @@
           <t>A4</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>4.179</v>
-      </c>
+      <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="9" t="n">
-        <v>67.821</v>
+        <v>72</v>
       </c>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
@@ -28251,7 +28241,7 @@
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n">
-        <v>43.934</v>
+        <v>45.124</v>
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -28264,7 +28254,7 @@
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n">
-        <v>11.066</v>
+        <v>9.875999999999999</v>
       </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
@@ -28303,16 +28293,14 @@
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n">
-        <v>6.791</v>
-      </c>
+      <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="8" t="n">
-        <v>53.209</v>
+        <v>60</v>
       </c>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
@@ -28361,10 +28349,10 @@
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n">
-        <v>45.946</v>
-      </c>
+      <c r="I9" s="9" t="n">
+        <v>45.695</v>
+      </c>
+      <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
@@ -28411,16 +28399,16 @@
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
+      <c r="H10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="O10" s="8" t="n"/>
       <c r="P10" s="8" t="n"/>
       <c r="Q10" s="8" t="n"/>
       <c r="R10" s="8" t="n"/>
@@ -28466,11 +28454,13 @@
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
+      <c r="L11" s="9" t="n">
+        <v>22.47</v>
+      </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n">
-        <v>28</v>
+        <v>5.53</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -28513,7 +28503,7 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>25</v>
+        <v>24.332</v>
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -28563,7 +28553,7 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n">
-        <v>84.416</v>
+        <v>86</v>
       </c>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
@@ -28615,11 +28605,11 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n">
-        <v>54.659</v>
-      </c>
+      <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="J14" s="8" t="n">
+        <v>54.999</v>
+      </c>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
@@ -28667,14 +28657,14 @@
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n">
-        <v>23.724</v>
+        <v>34.798</v>
       </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n">
-        <v>20.276</v>
+        <v>9.202</v>
       </c>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
@@ -28722,7 +28712,7 @@
       <c r="H16" s="8" t="n"/>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n">
-        <v>49.184</v>
+        <v>50</v>
       </c>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="8" t="n"/>
@@ -28773,13 +28763,15 @@
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n">
-        <v>23.614</v>
+        <v>21.826</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n"/>
+      <c r="O17" s="9" t="n">
+        <v>3.174</v>
+      </c>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
@@ -28822,12 +28814,12 @@
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n">
-        <v>56.926</v>
-      </c>
+      <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
+      <c r="L18" s="8" t="n">
+        <v>60</v>
+      </c>
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
@@ -28876,10 +28868,10 @@
       <c r="I19" s="9" t="n"/>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
@@ -28932,7 +28924,7 @@
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n">
-        <v>34.952</v>
+        <v>34.998</v>
       </c>
       <c r="Q20" s="8" t="n"/>
       <c r="R20" s="8" t="n"/>
@@ -28977,11 +28969,11 @@
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
@@ -29026,13 +29018,15 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
+      <c r="I22" s="8" t="n">
+        <v>4.022</v>
+      </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n">
-        <v>11.379</v>
+        <v>10.978</v>
       </c>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
@@ -29075,7 +29069,7 @@
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n">
-        <v>12.422</v>
+        <v>13</v>
       </c>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
@@ -29124,17 +29118,19 @@
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
+      <c r="E24" s="8" t="n">
+        <v>1.661</v>
+      </c>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="L24" s="8" t="n">
+        <v>13.339</v>
+      </c>
+      <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
@@ -29225,16 +29221,16 @@
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
+      <c r="K26" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
@@ -29814,11 +29810,13 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.6</v>
+        <v>0.311</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.289</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
